--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>130061541</v>
       </c>
       <c r="B3" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>130061541</v>
       </c>
       <c r="B3" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
